--- a/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-HealthcareService.xlsx
+++ b/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-HealthcareService.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T21:21:27+00:00</t>
+    <t>2026-10-11T19:39:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-HealthcareService.xlsx
+++ b/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-HealthcareService.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="321">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-11T19:39:36+00:00</t>
+    <t>2026-10-12T11:53:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -580,9 +580,6 @@
   </si>
   <si>
     <t>Collection of specialties handled by the service site. This is more of a medical term.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>https://fhir.hl7.at/core/r4/ValueSet/at-funktionscode-vs</t>
@@ -3047,11 +3044,11 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>182</v>
+        <v>108</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3092,10 +3089,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3118,13 +3115,13 @@
         <v>85</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3175,7 +3172,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3190,18 +3187,18 @@
         <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>189</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3224,13 +3221,13 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3281,7 +3278,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3296,7 +3293,7 @@
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>21</v>
@@ -3304,10 +3301,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3330,16 +3327,16 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3389,7 +3386,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3404,7 +3401,7 @@
         <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>21</v>
@@ -3412,10 +3409,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3438,13 +3435,13 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3495,7 +3492,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3510,7 +3507,7 @@
         <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
@@ -3518,10 +3515,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3544,13 +3541,13 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3601,7 +3598,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3616,7 +3613,7 @@
         <v>96</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
@@ -3624,10 +3621,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3650,16 +3647,16 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3709,7 +3706,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3724,7 +3721,7 @@
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
@@ -3732,10 +3729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3758,16 +3755,16 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3817,7 +3814,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3832,7 +3829,7 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
@@ -3840,10 +3837,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3869,13 +3866,13 @@
         <v>163</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3904,10 +3901,10 @@
         <v>167</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -3925,7 +3922,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3940,7 +3937,7 @@
         <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>21</v>
@@ -3948,10 +3945,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3974,13 +3971,13 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4031,7 +4028,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4054,10 +4051,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4080,13 +4077,13 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4137,7 +4134,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4152,7 +4149,7 @@
         <v>21</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>21</v>
@@ -4160,10 +4157,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4192,7 +4189,7 @@
         <v>131</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>133</v>
@@ -4245,7 +4242,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4260,7 +4257,7 @@
         <v>135</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
@@ -4268,14 +4265,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4297,10 +4294,10 @@
         <v>130</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>133</v>
@@ -4355,7 +4352,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4378,10 +4375,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4407,10 +4404,10 @@
         <v>163</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4440,7 +4437,7 @@
         <v>167</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>21</v>
@@ -4461,7 +4458,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4476,7 +4473,7 @@
         <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
@@ -4484,10 +4481,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4510,16 +4507,16 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4569,7 +4566,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4584,7 +4581,7 @@
         <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
@@ -4592,10 +4589,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4621,13 +4618,13 @@
         <v>163</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4656,11 +4653,11 @@
         <v>167</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="Z31" t="s" s="2">
-        <v>258</v>
-      </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
       </c>
@@ -4677,7 +4674,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4692,7 +4689,7 @@
         <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
@@ -4700,10 +4697,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4729,13 +4726,13 @@
         <v>163</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4764,7 +4761,7 @@
         <v>167</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>21</v>
@@ -4785,7 +4782,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4800,7 +4797,7 @@
         <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>21</v>
@@ -4808,10 +4805,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4837,13 +4834,13 @@
         <v>163</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4893,7 +4890,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -4916,10 +4913,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4945,10 +4942,10 @@
         <v>163</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4978,11 +4975,11 @@
         <v>167</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>273</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
       </c>
@@ -4999,7 +4996,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5014,7 +5011,7 @@
         <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
@@ -5022,10 +5019,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5051,10 +5048,10 @@
         <v>148</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5105,7 +5102,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5120,7 +5117,7 @@
         <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
@@ -5128,10 +5125,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5154,16 +5151,16 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5213,7 +5210,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5228,7 +5225,7 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>21</v>
@@ -5236,10 +5233,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5262,13 +5259,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5319,7 +5316,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5334,7 +5331,7 @@
         <v>21</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
@@ -5342,10 +5339,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5374,7 +5371,7 @@
         <v>131</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>133</v>
@@ -5427,7 +5424,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5442,7 +5439,7 @@
         <v>135</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
@@ -5450,14 +5447,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5479,10 +5476,10 @@
         <v>130</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>133</v>
@@ -5537,7 +5534,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5560,10 +5557,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5589,10 +5586,10 @@
         <v>104</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5619,14 +5616,14 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="Y40" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="Y40" t="s" s="2">
+      <c r="Z40" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>290</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
       </c>
@@ -5643,7 +5640,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5658,7 +5655,7 @@
         <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
@@ -5666,10 +5663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5695,10 +5692,10 @@
         <v>148</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5749,7 +5746,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5764,7 +5761,7 @@
         <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
@@ -5772,10 +5769,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5798,16 +5795,16 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5857,7 +5854,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5872,7 +5869,7 @@
         <v>96</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
@@ -5880,10 +5877,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5906,16 +5903,16 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>301</v>
-      </c>
       <c r="N43" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5965,7 +5962,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -5980,7 +5977,7 @@
         <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
@@ -5988,10 +5985,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6014,13 +6011,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6071,7 +6068,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6086,7 +6083,7 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
@@ -6094,10 +6091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6120,13 +6117,13 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6177,7 +6174,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6192,7 +6189,7 @@
         <v>21</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
@@ -6200,10 +6197,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6232,7 +6229,7 @@
         <v>131</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>133</v>
@@ -6285,7 +6282,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6300,7 +6297,7 @@
         <v>135</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
@@ -6308,14 +6305,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6337,10 +6334,10 @@
         <v>130</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>133</v>
@@ -6395,7 +6392,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6418,10 +6415,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6444,13 +6441,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6501,7 +6498,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>84</v>
@@ -6516,7 +6513,7 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
@@ -6524,10 +6521,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6550,13 +6547,13 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6607,7 +6604,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6622,7 +6619,7 @@
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
@@ -6630,10 +6627,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6656,13 +6653,13 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6713,7 +6710,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6728,7 +6725,7 @@
         <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
@@ -6736,10 +6733,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6762,13 +6759,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6819,7 +6816,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -6834,7 +6831,7 @@
         <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
